--- a/outputs/Block2_Validation_Stage_Contract_v12.xlsx
+++ b/outputs/Block2_Validation_Stage_Contract_v12.xlsx
@@ -55,7 +55,7 @@
     <t>Chosen family, hyperparameters and raw target predictions</t>
   </si>
   <si>
-    <t>Constrained 42 targets, derived identities and headline outcomes</t>
+    <t>DPP/RPP direct forecasts + downstream compatibility bridge</t>
   </si>
   <si>
     <t>Control probabilities and forecast distributions</t>
@@ -76,7 +76,7 @@
     <t>Observed election result as a correction</t>
   </si>
   <si>
-    <t>Writing simulated values back into the 42 targets</t>
+    <t>Writing simulated values back into DPP/RPP or race-first winners</t>
   </si>
 </sst>
 </file>
